--- a/product_selector_out/STM32G0x1.xlsx
+++ b/product_selector_out/STM32G0x1.xlsx
@@ -8508,7 +8508,7 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22242,7 +22242,7 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23223,7 +23223,7 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24204,7 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24858,7 +24858,7 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25185,7 +25185,7 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25839,7 +25839,7 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -35351,9 +35351,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -35571,14 +35571,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY34" s="8" t="inlineStr">
@@ -35651,9 +35651,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36005,9 +36005,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -36225,14 +36225,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW36" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY36" s="8" t="inlineStr">
@@ -36305,9 +36305,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36986,9 +36986,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -37206,14 +37206,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY39" s="8" t="inlineStr">
@@ -37286,9 +37286,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -37967,9 +37967,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -38187,14 +38187,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY42" s="8" t="inlineStr">
@@ -38267,9 +38267,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38621,9 +38621,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -38841,14 +38841,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW44" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY44" s="8" t="inlineStr">
@@ -38921,9 +38921,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38948,9 +38948,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -39168,14 +39168,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW45" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY45" s="8" t="inlineStr">
@@ -39248,9 +39248,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -39602,9 +39602,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -39822,14 +39822,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY47" s="8" t="inlineStr">
@@ -39902,9 +39902,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41891,9 +41891,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -42111,14 +42111,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY54" s="8" t="inlineStr">
@@ -42191,9 +42191,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43853,9 +43853,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -44073,14 +44073,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW60" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY60" s="8" t="inlineStr">
@@ -44153,9 +44153,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44180,9 +44180,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -44400,14 +44400,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY61" s="8" t="inlineStr">
@@ -44480,9 +44480,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45161,9 +45161,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -45381,14 +45381,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW64" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY64" s="8" t="inlineStr">
@@ -45461,9 +45461,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45488,9 +45488,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -45708,14 +45708,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW65" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY65" s="8" t="inlineStr">
@@ -45788,9 +45788,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46142,9 +46142,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -46362,14 +46362,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW67" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY67" s="8" t="inlineStr">
@@ -46442,9 +46442,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -46469,9 +46469,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -46689,14 +46689,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY68" s="8" t="inlineStr">
@@ -46769,9 +46769,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -48431,9 +48431,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -48651,14 +48651,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY74" s="8" t="inlineStr">
@@ -48731,9 +48731,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49085,9 +49085,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -49305,14 +49305,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY76" s="8" t="inlineStr">
@@ -49385,9 +49385,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50066,9 +50066,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -50286,14 +50286,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW79" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY79" s="8" t="inlineStr">
@@ -50366,9 +50366,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -51047,9 +51047,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -51267,14 +51267,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW82" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY82" s="8" t="inlineStr">
@@ -51347,9 +51347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -51374,9 +51374,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -51594,14 +51594,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW83" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY83" s="8" t="inlineStr">
@@ -51674,9 +51674,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -51701,9 +51701,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -51921,14 +51921,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW84" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY84" s="8" t="inlineStr">
@@ -52001,9 +52001,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -52028,9 +52028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -52248,14 +52248,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW85" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY85" s="8" t="inlineStr">
@@ -52328,9 +52328,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -52355,9 +52355,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -52575,14 +52575,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY86" s="8" t="inlineStr">
@@ -52655,9 +52655,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -52682,9 +52682,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -52902,14 +52902,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW87" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY87" s="8" t="inlineStr">
@@ -52982,9 +52982,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54638,7 +54638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -54687,7 +54687,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -54731,7 +54731,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -54775,7 +54775,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -54819,7 +54819,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -54863,7 +54863,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -54907,7 +54907,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -54951,7 +54951,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -54995,7 +54995,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55039,7 +55039,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55083,7 +55083,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55127,7 +55127,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55171,7 +55171,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55215,7 +55215,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55259,7 +55259,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55303,7 +55303,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55347,7 +55347,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55391,7 +55391,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55435,7 +55435,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55479,7 +55479,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55523,7 +55523,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55567,7 +55567,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55611,7 +55611,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -55640,7 +55640,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32G0B1KB</t>
+          <t>STM32G0B1CB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -55655,14 +55655,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G0B1CB</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -55677,19 +55677,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G0C1RE</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -55699,14 +55699,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -55721,14 +55721,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -55750,7 +55750,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -55765,14 +55765,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -55794,7 +55794,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G0C1VE</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -55809,19 +55809,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -55831,19 +55831,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -55853,19 +55853,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -55875,19 +55875,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -55897,19 +55897,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G0B1RB</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -55919,14 +55919,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -55941,14 +55941,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -55970,7 +55970,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G0C1ME</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -55985,19 +55985,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G0C1KE</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -56007,14 +56007,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -56029,14 +56029,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -56058,7 +56058,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G0C1CE</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -56073,19 +56073,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -56095,19 +56095,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -56117,19 +56117,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -56139,19 +56139,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -56161,19 +56161,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -56183,19 +56183,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -56205,19 +56205,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -56227,19 +56227,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -56249,19 +56249,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -56271,19 +56271,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -56293,19 +56293,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -56315,19 +56315,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -56337,19 +56337,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G0B1MC</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -56359,14 +56359,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G0C1CC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -56381,19 +56381,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -56403,19 +56403,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -56425,19 +56425,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -56447,19 +56447,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -56469,19 +56469,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -56491,19 +56491,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -56513,19 +56513,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -56535,19 +56535,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G0C1CC</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -56557,14 +56557,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G0C1KC</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -56579,19 +56579,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G0B1RE</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -56601,14 +56601,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G0B1CC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -56623,19 +56623,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -56645,19 +56645,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -56667,19 +56667,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -56689,19 +56689,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32G0B1VE</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -56711,14 +56711,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32G0B1NE</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -56733,19 +56733,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -56755,19 +56755,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -56777,19 +56777,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32G0B1ME</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -56799,14 +56799,14 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32G0B1KC</t>
+          <t>STM32G071RB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -56821,19 +56821,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G071RB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -56843,19 +56843,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G051F6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -56865,19 +56865,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G051F6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -56887,19 +56887,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G051G6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -56909,19 +56909,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32G0B1CC</t>
+          <t>STM32G051G6</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -56931,14 +56931,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G041K6</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -56953,14 +56953,14 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G041K6</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -56982,7 +56982,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G041G6</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -56997,14 +56997,14 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G041G6</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -57026,7 +57026,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32G0B1RC</t>
+          <t>STM32G071EB</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -57041,19 +57041,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G071EB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -57063,19 +57063,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G031Y8</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -57085,19 +57085,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32G0B1VC</t>
+          <t>STM32G031Y8</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -57107,14 +57107,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G041Y8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -57129,14 +57129,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G041Y8</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -57150,512 +57150,6 @@
         </is>
       </c>
       <c r="D114" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>STM32G071RB</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>STM32G071RB</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>STM32G0B1CE</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM32G051F6</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM32G051F6</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM32G051G6</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>STM32G051G6</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>STM32G0C1RC</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>STM32G0B1VB</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>STM32G0C1VC</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>STM32G0C1MC</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>STM32G0B1KE</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>STM32G0B1MB</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>STM32G041K6</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>STM32G041K6</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>STM32G041G6</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>STM32G041G6</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>STM32G071EB</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>STM32G071EB</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>STM32G031Y8</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>STM32G031Y8</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>STM32G041Y8</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>STM32G041Y8</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
         <is>
           <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>

--- a/product_selector_out/STM32G0x1.xlsx
+++ b/product_selector_out/STM32G0x1.xlsx
@@ -8508,7 +8508,7 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -11778,7 +11778,7 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -12105,7 +12105,7 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -22242,7 +22242,7 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -23223,7 +23223,7 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24204,7 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -24858,7 +24858,7 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -25185,7 +25185,7 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -25839,7 +25839,7 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
         </is>
       </c>
     </row>
@@ -35351,9 +35351,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
@@ -35571,14 +35571,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY34" s="8" t="inlineStr">
@@ -35651,9 +35651,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -36005,9 +36005,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -36225,14 +36225,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY36" s="8" t="inlineStr">
@@ -36305,9 +36305,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM36" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -36986,9 +36986,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -37206,14 +37206,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY39" s="8" t="inlineStr">
@@ -37286,9 +37286,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -37967,9 +37967,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -38187,14 +38187,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX42" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY42" s="8" t="inlineStr">
@@ -38267,9 +38267,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -38621,9 +38621,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -38841,14 +38841,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX44" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX44" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY44" s="8" t="inlineStr">
@@ -38921,9 +38921,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM44" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -38948,9 +38948,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
@@ -39168,14 +39168,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX45" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX45" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY45" s="8" t="inlineStr">
@@ -39248,9 +39248,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM45" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -39602,9 +39602,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
@@ -39822,14 +39822,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX47" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX47" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY47" s="8" t="inlineStr">
@@ -39902,9 +39902,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM47" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -41891,9 +41891,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -42111,14 +42111,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX54" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY54" s="8" t="inlineStr">
@@ -42191,9 +42191,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -43853,9 +43853,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -44073,14 +44073,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX60" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX60" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY60" s="8" t="inlineStr">
@@ -44153,9 +44153,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM60" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44180,9 +44180,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -44400,14 +44400,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX61" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY61" s="8" t="inlineStr">
@@ -44480,9 +44480,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -45161,9 +45161,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -45381,14 +45381,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX64" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY64" s="8" t="inlineStr">
@@ -45461,9 +45461,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -45488,9 +45488,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
@@ -45708,14 +45708,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX65" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY65" s="8" t="inlineStr">
@@ -45788,9 +45788,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -46142,9 +46142,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -46362,14 +46362,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX67" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY67" s="8" t="inlineStr">
@@ -46442,9 +46442,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -46469,9 +46469,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -46689,14 +46689,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX68" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY68" s="8" t="inlineStr">
@@ -46769,9 +46769,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -48431,9 +48431,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -48651,14 +48651,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX74" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY74" s="8" t="inlineStr">
@@ -48731,9 +48731,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -49085,9 +49085,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -49305,14 +49305,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX76" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY76" s="8" t="inlineStr">
@@ -49385,9 +49385,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -50066,9 +50066,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
@@ -50286,14 +50286,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX79" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY79" s="8" t="inlineStr">
@@ -50366,9 +50366,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -51047,9 +51047,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -51267,14 +51267,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW82" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY82" s="8" t="inlineStr">
@@ -51347,9 +51347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -51374,9 +51374,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
@@ -51594,14 +51594,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX83" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY83" s="8" t="inlineStr">
@@ -51674,9 +51674,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -51701,9 +51701,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -51921,14 +51921,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW84" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX84" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY84" s="8" t="inlineStr">
@@ -52001,9 +52001,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -52028,9 +52028,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
@@ -52248,14 +52248,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX85" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX85" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY85" s="8" t="inlineStr">
@@ -52328,9 +52328,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM85" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -52355,9 +52355,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -52575,14 +52575,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY86" s="8" t="inlineStr">
@@ -52655,9 +52655,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -52682,9 +52682,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
@@ -52902,14 +52902,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX87" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY87" s="8" t="inlineStr">
@@ -52982,9 +52982,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -54638,7 +54638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D114"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -55640,7 +55640,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32G0B1CB</t>
+          <t>STM32G0B1KB</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -55662,7 +55662,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G0B1CB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -55677,19 +55677,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G0C1RE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -55699,14 +55699,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -55728,7 +55728,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -55750,7 +55750,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -55772,7 +55772,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -55794,7 +55794,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G0C1VE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -55809,19 +55809,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -55831,19 +55831,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -55853,19 +55853,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -55875,19 +55875,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -55897,19 +55897,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G0B1RB</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -55919,14 +55919,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -55948,7 +55948,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -55970,7 +55970,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G0C1ME</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -55985,19 +55985,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G0C1KE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -56007,14 +56007,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -56036,7 +56036,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -56058,7 +56058,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G0C1CE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -56073,19 +56073,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -56095,19 +56095,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -56117,19 +56117,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -56139,19 +56139,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -56161,19 +56161,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -56183,19 +56183,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -56205,19 +56205,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -56227,19 +56227,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -56249,19 +56249,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -56271,19 +56271,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -56293,19 +56293,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -56315,19 +56315,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -56337,19 +56337,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G0B1MC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -56359,14 +56359,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G0C1CC</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -56381,19 +56381,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -56403,19 +56403,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -56425,19 +56425,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -56447,19 +56447,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -56469,19 +56469,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -56491,19 +56491,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -56513,19 +56513,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -56535,19 +56535,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G0C1CC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -56557,14 +56557,14 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G0C1KC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -56579,19 +56579,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G0B1RE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -56601,14 +56601,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32G0B1CC</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -56623,19 +56623,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -56645,19 +56645,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -56667,19 +56667,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -56689,19 +56689,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G0B1VE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -56711,14 +56711,14 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G0B1NE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -56733,19 +56733,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -56755,19 +56755,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -56777,19 +56777,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G0B1ME</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -56799,14 +56799,14 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32G071RB</t>
+          <t>STM32G0B1KC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -56821,19 +56821,19 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32G071RB</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -56843,19 +56843,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32G051F6</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -56865,19 +56865,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32G051F6</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -56887,19 +56887,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32G051G6</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -56909,19 +56909,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32G051G6</t>
+          <t>STM32G0B1CC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -56931,14 +56931,14 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32G041K6</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -56960,7 +56960,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32G041K6</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -56982,7 +56982,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32G041G6</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -57004,7 +57004,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32G041G6</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -57026,7 +57026,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32G071EB</t>
+          <t>STM32G0B1RC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -57041,19 +57041,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32G071EB</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -57063,19 +57063,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32G031Y8</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -57085,19 +57085,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32G031Y8</t>
+          <t>STM32G0B1VC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -57107,14 +57107,14 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32G041Y8</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -57136,20 +57136,526 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>STM32G041G8</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STM32G071RB</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32G071RB</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32G0B1CE</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32G051F6</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32G051F6</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32G051G6</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32G051G6</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32G0C1RC</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32G0B1VB</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32G0C1VC</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32G0C1MC</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>STM32G0B1KE</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32G0B1MB</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32G041K6</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32G041K6</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32G041G6</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32G041G6</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32G071EB</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32G071EB</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32G031Y8</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32G031Y8</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
           <t>STM32G041Y8</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STM32G041Y8</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
         <is>
           <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>

--- a/product_selector_out/STM32G0x1.xlsx
+++ b/product_selector_out/STM32G0x1.xlsx
@@ -8508,7 +8508,7 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -17337,7 +17337,7 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -19299,7 +19299,7 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19626,7 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -20607,7 +20607,7 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -21588,7 +21588,7 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -22242,7 +22242,7 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -23223,7 +23223,7 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -25839,7 +25839,7 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g0b1cc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="BM92" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -35416,14 +35416,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
@@ -35571,19 +35571,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="9" t="inlineStr">
+      <c r="AW34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX34" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY34" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY34" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ34" s="6" t="inlineStr">
@@ -38032,14 +38032,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S42" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T42" s="6" t="inlineStr">
@@ -38187,19 +38187,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="9" t="inlineStr">
+      <c r="AW42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX42" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY42" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY42" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ42" s="6" t="inlineStr">
@@ -41956,14 +41956,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T54" s="6" t="inlineStr">
@@ -42111,19 +42111,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="9" t="inlineStr">
+      <c r="AW54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY54" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY54" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ54" s="6" t="inlineStr">
@@ -44245,14 +44245,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S61" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T61" s="6" t="inlineStr">
@@ -44400,19 +44400,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="9" t="inlineStr">
+      <c r="AW61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX61" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY61" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY61" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ61" s="6" t="inlineStr">
@@ -45226,14 +45226,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S64" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T64" s="6" t="inlineStr">
@@ -45381,19 +45381,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW64" s="9" t="inlineStr">
+      <c r="AW64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX64" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY64" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY64" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ64" s="6" t="inlineStr">
@@ -45553,14 +45553,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S65" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T65" s="6" t="inlineStr">
@@ -45708,19 +45708,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW65" s="9" t="inlineStr">
+      <c r="AW65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX65" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY65" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY65" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ65" s="6" t="inlineStr">
@@ -46207,14 +46207,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S67" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T67" s="6" t="inlineStr">
@@ -46362,19 +46362,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW67" s="9" t="inlineStr">
+      <c r="AW67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX67" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY67" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY67" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ67" s="6" t="inlineStr">
@@ -46534,14 +46534,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S68" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T68" s="6" t="inlineStr">
@@ -46689,19 +46689,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="9" t="inlineStr">
+      <c r="AW68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX68" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY68" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY68" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ68" s="6" t="inlineStr">
@@ -47515,14 +47515,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -47670,19 +47670,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW71" s="9" t="inlineStr">
+      <c r="AW71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY71" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY71" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ71" s="6" t="inlineStr">
@@ -48496,14 +48496,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S74" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T74" s="6" t="inlineStr">
@@ -48651,19 +48651,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="9" t="inlineStr">
+      <c r="AW74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX74" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY74" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY74" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ74" s="6" t="inlineStr">
@@ -49150,14 +49150,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S76" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T76" s="6" t="inlineStr">
@@ -49305,19 +49305,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="9" t="inlineStr">
+      <c r="AW76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX76" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY76" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY76" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ76" s="6" t="inlineStr">
@@ -50131,14 +50131,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S79" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T79" s="6" t="inlineStr">
@@ -50286,19 +50286,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW79" s="9" t="inlineStr">
+      <c r="AW79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX79" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY79" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY79" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ79" s="6" t="inlineStr">
@@ -51439,14 +51439,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S83" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T83" s="6" t="inlineStr">
@@ -51594,19 +51594,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW83" s="9" t="inlineStr">
+      <c r="AW83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX83" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY83" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY83" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ83" s="6" t="inlineStr">
@@ -52420,14 +52420,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T86" s="6" t="inlineStr">
@@ -52575,19 +52575,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="9" t="inlineStr">
+      <c r="AW86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY86" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY86" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ86" s="6" t="inlineStr">
@@ -52747,14 +52747,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S87" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T87" s="6" t="inlineStr">
@@ -52902,19 +52902,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW87" s="9" t="inlineStr">
+      <c r="AW87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX87" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY87" s="9" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY87" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ87" s="6" t="inlineStr">
@@ -54317,9 +54317,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
@@ -54537,19 +54537,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW92" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AY92" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AW92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX92" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
       <c r="AZ92" s="8" t="inlineStr">
@@ -54617,9 +54617,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM92" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54638,7 +54638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -55645,7 +55645,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -55655,19 +55655,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32G0B1CB</t>
+          <t>STM32G0B1KB</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -55677,19 +55677,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32G0C1RE</t>
+          <t>STM32G0B1KB</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -55699,14 +55699,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G0B1CB</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -55721,19 +55721,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32G071KB</t>
+          <t>STM32G0C1RE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -55743,14 +55743,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -55772,7 +55772,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32G031C6</t>
+          <t>STM32G071KB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -55794,7 +55794,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32G0C1VE</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -55809,19 +55809,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G031C6</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -55831,19 +55831,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32G071CB</t>
+          <t>STM32G0C1VE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -55853,14 +55853,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -55882,7 +55882,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32G071R8</t>
+          <t>STM32G071CB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -55904,7 +55904,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32G0B1RB</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -55919,19 +55919,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G071R8</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -55941,19 +55941,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32G071GB</t>
+          <t>STM32G0B1RB</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -55963,19 +55963,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32G0C1ME</t>
+          <t>STM32G0B1RB</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -55985,19 +55985,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32G0C1KE</t>
+          <t>STM32G0B1RB</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -56007,14 +56007,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -56036,7 +56036,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32G031G8</t>
+          <t>STM32G071GB</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -56058,7 +56058,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32G0C1CE</t>
+          <t>STM32G0C1ME</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -56080,7 +56080,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G0C1KE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -56095,19 +56095,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32G031C8</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -56117,19 +56117,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G031G8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -56139,19 +56139,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32G051C8</t>
+          <t>STM32G0C1CE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -56161,14 +56161,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -56190,7 +56190,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32G051K8</t>
+          <t>STM32G031C8</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -56212,7 +56212,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -56234,7 +56234,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32G051C6</t>
+          <t>STM32G051C8</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -56256,7 +56256,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -56278,7 +56278,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32G031G4</t>
+          <t>STM32G051K8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -56300,7 +56300,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -56322,7 +56322,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32G041K8</t>
+          <t>STM32G051C6</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -56344,7 +56344,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32G0B1MC</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -56359,19 +56359,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G031G4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -56381,19 +56381,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32G031F4</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -56403,19 +56403,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G041K8</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -56425,19 +56425,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32G051K6</t>
+          <t>STM32G0B1MC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -56447,19 +56447,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G0B1MC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -56469,14 +56469,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32G051G8</t>
+          <t>STM32G0B1MC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -56491,14 +56491,14 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -56520,7 +56520,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32G051F8</t>
+          <t>STM32G031F4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -56542,7 +56542,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32G0C1CC</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -56557,19 +56557,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32G0C1KC</t>
+          <t>STM32G051K6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -56579,14 +56579,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32G0B1RE</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -56601,19 +56601,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G051G8</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -56623,19 +56623,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32G081EB</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -56645,19 +56645,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G051F8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -56667,19 +56667,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32G031F8</t>
+          <t>STM32G0C1CC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -56689,14 +56689,14 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32G0B1VE</t>
+          <t>STM32G0C1KC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -56718,12 +56718,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32G0B1NE</t>
+          <t>STM32G0B1RE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -56733,19 +56733,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G0B1RE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -56755,14 +56755,14 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32G031K8</t>
+          <t>STM32G0B1RE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -56777,14 +56777,14 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32G0B1ME</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -56799,19 +56799,19 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32G0B1KC</t>
+          <t>STM32G081EB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -56821,14 +56821,14 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -56850,7 +56850,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32G081CB</t>
+          <t>STM32G031F8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -56872,12 +56872,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G0B1VE</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -56887,19 +56887,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32G081RB</t>
+          <t>STM32G0B1VE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -56909,19 +56909,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32G0B1CC</t>
+          <t>STM32G0B1VE</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -56931,19 +56931,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G0B1NE</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -56953,19 +56953,19 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32G081GB</t>
+          <t>STM32G0B1NE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -56975,19 +56975,19 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G0B1NE</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -56997,19 +56997,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32G041F8</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -57019,19 +57019,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32G0B1RC</t>
+          <t>STM32G031K8</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -57041,19 +57041,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G0B1ME</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -57063,19 +57063,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32G081KB</t>
+          <t>STM32G0B1ME</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -57085,19 +57085,19 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32G0B1VC</t>
+          <t>STM32G0B1ME</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -57107,19 +57107,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G0B1KC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -57129,19 +57129,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32G041G8</t>
+          <t>STM32G0B1KC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -57151,19 +57151,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32G071RB</t>
+          <t>STM32G0B1KC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -57173,19 +57173,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32G071RB</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -57195,19 +57195,19 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32G0B1CE</t>
+          <t>STM32G081CB</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -57217,14 +57217,14 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32G051F6</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -57246,7 +57246,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32G051F6</t>
+          <t>STM32G081RB</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -57268,12 +57268,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32G051G6</t>
+          <t>STM32G0B1CC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -57283,19 +57283,19 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32G051G6</t>
+          <t>STM32G0B1CC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -57305,19 +57305,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32G0C1RC</t>
+          <t>STM32G0B1CC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -57327,14 +57327,14 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32G0B1VB</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -57349,19 +57349,19 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32G0C1VC</t>
+          <t>STM32G081GB</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -57371,14 +57371,14 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32G0C1MC</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -57393,19 +57393,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32G0B1KE</t>
+          <t>STM32G041F8</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -57415,19 +57415,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32G0B1MB</t>
+          <t>STM32G0B1RC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -57437,19 +57437,19 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32G041K6</t>
+          <t>STM32G0B1RC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -57459,14 +57459,14 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32G041K6</t>
+          <t>STM32G0B1RC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -57481,14 +57481,14 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32G041G6</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -57510,7 +57510,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32G041G6</t>
+          <t>STM32G081KB</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -57532,12 +57532,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32G071EB</t>
+          <t>STM32G0B1VC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -57547,19 +57547,19 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32G071EB</t>
+          <t>STM32G0B1VC</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -57569,19 +57569,19 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32G031Y8</t>
+          <t>STM32G0B1VC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -57591,19 +57591,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32G031Y8</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+          <t>Supply Voltage (V) min</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -57613,19 +57613,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32G041Y8</t>
+          <t>STM32G041G8</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Supply Voltage (V) min</t>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -57635,27 +57635,643 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32G041Y8</t>
+          <t>STM32G071RB</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STM32G071RB</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
           <t>Supply Current (µA) (@ Lowest Power) typ</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STM32G0B1CE</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>STM32G0B1CE</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>STM32G0B1CE</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STM32G051F6</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>STM32G051F6</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>STM32G051G6</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>STM32G051G6</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>STM32G0C1RC</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>STM32G0B1VB</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>STM32G0B1VB</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>STM32G0B1VB</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>STM32G0C1VC</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>STM32G0C1MC</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>STM32G0B1KE</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>STM32G0B1KE</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>STM32G0B1KE</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>STM32G0B1MB</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>STM32G0B1MB</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Table 6. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>STM32G0B1MB</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Table 27. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>STM32G041K6</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>STM32G041K6</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>STM32G041G6</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>STM32G041G6</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>STM32G071EB</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>STM32G071EB</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Table 25. Current consumption in Run and Low-power run modes</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>STM32G031Y8</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Table 21. General operating conditions: V_DD min reads '1.7(1)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>STM32G031Y8</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Supply Current (µA) (@ Lowest Power) typ</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
         <is>
           <t>Table 25. Current consumption in Run and Low-power run modes</t>
         </is>

--- a/product_selector_out/STM32G0x1.xlsx
+++ b/product_selector_out/STM32G0x1.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM92"/>
+  <dimension ref="A1:BN92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.08203125" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g061c6.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b1cb.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -10470,6 +10617,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -10797,6 +10949,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -11124,6 +11281,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -11451,6 +11613,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -12432,6 +12609,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -15048,6 +15265,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -15702,6 +15929,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -16029,6 +16261,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -16356,6 +16593,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -16683,6 +16925,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -17010,6 +17257,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -17337,6 +17589,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -17664,6 +17921,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g081cb.pdf</t>
         </is>
       </c>
@@ -17991,6 +18253,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -18318,6 +18585,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -18645,6 +18917,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -18972,6 +19249,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -19299,6 +19581,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -19626,6 +19913,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -19953,6 +20245,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g081cb.pdf</t>
         </is>
       </c>
@@ -20280,6 +20577,11 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g081cb.pdf</t>
         </is>
       </c>
@@ -20607,6 +20909,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -20934,6 +21241,11 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g081cb.pdf</t>
         </is>
       </c>
@@ -21261,6 +21573,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -21588,6 +21905,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -21915,6 +22237,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g081cb.pdf</t>
         </is>
       </c>
@@ -22242,6 +22569,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -22569,6 +22901,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -22896,6 +23233,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -23223,6 +23565,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -23550,6 +23897,11 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -23877,6 +24229,11 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g051c6.pdf</t>
         </is>
       </c>
@@ -24204,6 +24561,11 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -24531,6 +24893,11 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -24858,6 +25225,11 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -25185,6 +25557,11 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0c1cc.pdf</t>
         </is>
       </c>
@@ -25512,6 +25889,11 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN86" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -25839,6 +26221,11 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g0b0ce.pdf</t>
         </is>
       </c>
@@ -26166,6 +26553,11 @@
       </c>
       <c r="BM88" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -26493,6 +26885,11 @@
       </c>
       <c r="BM89" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g041c6.pdf</t>
         </is>
       </c>
@@ -26820,6 +27217,11 @@
       </c>
       <c r="BM90" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g071c8.pdf</t>
         </is>
       </c>
@@ -27147,6 +27549,11 @@
       </c>
       <c r="BM91" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32g031c4.pdf</t>
         </is>
       </c>
@@ -27477,9 +27884,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN92" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -27500,16 +27912,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -27522,6 +27932,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -27541,7 +27952,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -27639,7 +28052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM92"/>
+  <dimension ref="A1:BN92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -27707,6 +28120,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28040,6 +28454,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -28135,6 +28554,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -28457,7 +28877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28784,7 +29209,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29111,7 +29541,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29438,7 +29873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29765,7 +30205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30092,7 +30537,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30419,7 +30869,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30746,7 +31201,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31073,7 +31533,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31400,7 +31865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31727,7 +32197,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32054,7 +32529,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32381,7 +32861,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32708,7 +33193,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33035,7 +33525,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33362,7 +33857,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33689,7 +34189,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34016,7 +34521,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34343,7 +34853,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34670,7 +35185,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34997,7 +35517,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35324,7 +35849,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35651,7 +36181,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35978,7 +36513,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36305,7 +36845,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36632,7 +37177,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36959,7 +37509,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37286,7 +37841,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37613,7 +38173,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37940,7 +38505,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38267,7 +38837,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38594,7 +39169,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38921,7 +39501,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39248,7 +39833,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39575,7 +40165,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39902,7 +40497,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40229,7 +40829,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40556,7 +41161,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40883,7 +41493,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41210,7 +41825,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41537,7 +42157,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41864,7 +42489,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42191,7 +42821,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42518,7 +43153,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42845,7 +43485,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43172,7 +43817,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43499,7 +44149,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43826,7 +44481,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44153,7 +44813,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44480,7 +45145,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44807,7 +45477,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45134,7 +45809,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45461,7 +46141,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45788,7 +46473,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46115,7 +46805,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46442,7 +47137,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46769,7 +47469,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47096,7 +47801,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47423,7 +48133,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
+      <c r="BM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47750,7 +48465,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48077,7 +48797,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48404,7 +49129,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48731,7 +49461,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49058,7 +49793,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49385,7 +50125,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49712,7 +50457,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50039,7 +50789,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50366,7 +51121,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50693,7 +51453,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51020,7 +51785,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51347,7 +52117,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51674,7 +52449,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52001,7 +52781,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52328,7 +53113,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52655,7 +53445,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
+      <c r="BM86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN86" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52982,7 +53777,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="6" t="inlineStr">
+      <c r="BM87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53309,7 +54109,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM88" s="6" t="inlineStr">
+      <c r="BM88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53636,7 +54441,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM89" s="6" t="inlineStr">
+      <c r="BM89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53963,7 +54773,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM90" s="6" t="inlineStr">
+      <c r="BM90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54290,7 +55105,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM91" s="6" t="inlineStr">
+      <c r="BM91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54622,11 +55442,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
